--- a/templates/Experiments RNA.xlsx
+++ b/templates/Experiments RNA.xlsx
@@ -29,9 +29,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A reference to one or more individuals
-associated to the process
- Select one or more items from
+          <t>Select one or more items from
 Individuals</t>
         </r>
       </text>
@@ -45,10 +43,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>One or more characters used to identify,
-name, or characterize the nature,
-properties, or contents of a sample
- Select one item from Sample identifiers</t>
+          <t>Select one item from Sample identifiers</t>
         </r>
       </text>
     </comment>
@@ -61,10 +56,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>An identifier associated with a
-particular source, used by the data
-provider or owner
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -77,9 +69,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>One or more associations between the
-individual and an organisation.
- Select one or more items from
+          <t>Select one or more items from
 Organisations</t>
         </r>
       </text>
@@ -93,9 +83,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A reference to a related sample (e.g., a
-srDNA sample) used in this experiment
- Select one item from Sample identifiers</t>
+          <t>Select one item from Sample identifiers</t>
         </r>
       </text>
     </comment>
@@ -108,9 +96,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The sample batch lot identifier in which
-the sample was sequenced
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -123,10 +109,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A data field which describes the name of
-the third party company or laboratory
-that provided services.
- Select one item from Organisations</t>
+          <t>Select one item from Organisations</t>
         </r>
       </text>
     </comment>
@@ -139,8 +122,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>E.g. genomic source
- Select one item from Library source</t>
+          <t>Select one item from Library source</t>
         </r>
       </text>
     </comment>
@@ -153,8 +135,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>E.g. RANDOM method
- Select one item from Library selection</t>
+          <t>Select one item from Library selection</t>
         </r>
       </text>
     </comment>
@@ -167,8 +148,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Either PAIRED or SINGLE
- Select one item from Library layout</t>
+          <t>Select one item from Library layout</t>
         </r>
       </text>
     </comment>
@@ -181,10 +161,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The manufacturer's name for the kit used
-to construct a genomic library using
-target capture-based techniques
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -197,16 +174,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Indicates which target enrichment kit
-was used to prepare this sample. Target
-enrichment is a pre-sequencing DNA
-preparation step where DNA sequences are
-either directly amplified (amplicon or
-multiplex PCR-based) or captured (hybrid
-capture-based) in order to only focus on
-specific regions of a genome or DNA
-sample.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -219,9 +187,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The vendor name for the nucleotide
-sequencing library preparation kit.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -234,16 +200,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Pre-filled, ready-to-use reagent
-cartridges intented to improve
-chemistry, cluster density and read
-length as well as improve quality (Q)
-scores for this sample. Reagent
-components are encoded to interact with
-the sequencing system to validate
-compatibility with user-defined
-applications.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -256,10 +213,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A machine-readable representation of an
-instrument (e.g., a sequencer) in a
-visual format on a surface
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -272,13 +226,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Indicates whether any unique molecular
-identifiers (UMIs) are present. An UMI
-barcode is a short nucleotide sequence
-that is used to identify reads
-originating from an individual mRNA
-molecule.
- Select TRUE or FALSE</t>
+          <t>Select TRUE or FALSE</t>
         </r>
       </text>
     </comment>
@@ -291,10 +239,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A laboratory process in which RNA
-molecules are broken into smaller
-fragments
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -307,11 +252,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The name of the sequencing platform
-(i.e. brand, name of a company that
-produces sequencer equipment). In FAIR
-Genomes: SequencingPlatform.
- Select one item from Sequencing
+          <t>Select one item from Sequencing
 platforms</t>
         </r>
       </text>
@@ -325,11 +266,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The name of the product and model number
-of a manufacturer's genomic (dna)
-sequencer. In FAIR Genomes:
-SequencingInstrumentModel.
- Select one item from Sequencing
+          <t>Select one item from Sequencing
 instrument models</t>
         </r>
       </text>
@@ -343,8 +280,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>When the sequencing run took place
- DATETIME</t>
+          <t>DATETIME (yyyy-mm-dd hh:mm:ss)</t>
         </r>
       </text>
     </comment>
@@ -357,11 +293,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A flow cell identifier is an identifier
-that identifies some flow cell (aparatus
-in the fluidic subsystem where the
-sheath and sample meet)
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -374,12 +306,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Can be one of several types; jet-in-air,
-quartz cuvette, or a hybrid of the two.
-The sample flows through the center of a
-fluid column of sheath fluid in the flow
-cell.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -392,13 +319,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The unique number assigned to an
-instrument (e.g., a sequencer). This
-could either be the serial number, a
-unique ID generated by the data
-provider/owner, or another character
-string used to identify the instrument
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -411,9 +332,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The source-specific version of the
-published genome assembly.
- Select one item from Genome accessions</t>
+          <t>Select one item from Genome accessions</t>
         </r>
       </text>
     </comment>
@@ -426,10 +345,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A sequence of characters used to
-uniquely identify a particular run of a
-test on a particular batch of samples
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -442,16 +358,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>In paired-end sequencing, the DNA
-between the adapter sequences is the
-insert. The length of this sequence is
-known as the insert size, not to be
-confused with the inner distance between
-reads. So, fragment length equals read
-adapter length (2x) plus insert size,
-and insert size equals read lenght (2x)
-plus inner distance.
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -464,11 +371,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The number of nucleotides intended to be
-ordered from each side of a nucleic acid
-fragment obtained after the completion
-of a sequencing process.
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -481,9 +384,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The total expected number of read pairs,
-e.g., 80 M
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -496,9 +397,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A written explanation, observation or
-criticism added to textual material
- TEXT</t>
+          <t>TEXT</t>
         </r>
       </text>
     </comment>
